--- a/results/result_evaluation_logs/H_Full-Network-Architecture_Gen2.xlsx
+++ b/results/result_evaluation_logs/H_Full-Network-Architecture_Gen2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -626,11 +621,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7b474c4a-5bfa-48fb-b595-6a416052c6e4</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -706,11 +696,6 @@
 wd:Q20992419 wd:P136 wd:Q17516 .
 wd:Q20992419 wd:P2348 wd:Q120 .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>b13a657f-0d7b-4b1a-b879-b9ac0359d690</t>
         </is>
       </c>
     </row>
@@ -792,11 +777,6 @@
 </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>f60db107-35ab-46dd-8f2e-270c7d4da116</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -875,11 +855,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>05324042-340a-4944-8e71-dff541d63ab8</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -956,11 +931,6 @@
 </t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>641678d7-c3cc-4a20-85e8-0cb6d8150457</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1035,11 +1005,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt;.
 wd:Q506252 wd:P31 wd:Q279014 .
 </t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6295e8ee-91cc-48be-adb3-5284e11da0bc</t>
         </is>
       </c>
     </row>
@@ -1117,11 +1082,6 @@
 wd:Q2226643 wd:P138 wd:Q28937 .
 wd:Q2226643 wd:P31 wd:Q65943 .
 </t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1d87fba8-9e45-4461-892e-207219043003</t>
         </is>
       </c>
     </row>
@@ -1203,11 +1163,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>69a96457-a65a-4f66-b51b-21f056bd1b5f</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1253,10 +1208,10 @@
         <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
@@ -1290,11 +1245,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>854c7e6b-d85b-45aa-92b7-119cb4133e6f</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1375,11 +1325,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5e5c5d5b-19d9-43c0-9ca8-acded817a21d</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1457,11 +1402,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>e11bbcd6-fba0-4b68-b448-fd0bcf5fde4e</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1535,11 +1475,6 @@
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt;.
 </t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>3c572f42-bdc9-4a8c-8d87-155af38ea108</t>
         </is>
       </c>
     </row>
@@ -1621,11 +1556,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>a6d3623a-84e0-4dd6-82fe-a6e05e745557</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1674,7 +1604,7 @@
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>4</v>
@@ -1705,11 +1635,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>89f728ae-de97-482a-af2e-c8845b5a0eea</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1786,11 +1711,6 @@
 </t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>274286b5-f997-4623-b055-28bfa7513950</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1868,11 +1788,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>1bdaec36-0691-4f5e-8983-840aa264a520</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1948,11 +1863,6 @@
 wd:Q607380 wd:P5588 wd:Q782 .
 wd:Q607380 wd:P183 wd:Q664 .
 </t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>b9bf5426-8b4d-42b5-90e4-4e816e8c8fb0</t>
         </is>
       </c>
     </row>
@@ -2037,11 +1947,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>1bc75193-9fd4-47ed-9a57-297799949288</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2116,11 +2021,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt;.
 wd:Q20671544 wd:P106 wd:Q27914 .
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>08664702-759e-409f-91f2-790ec70691cd</t>
         </is>
       </c>
     </row>
@@ -2205,11 +2105,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>98dcca74-db2c-42f4-9bb2-66fae9371599</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2286,11 +2181,6 @@
 </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>818b9efd-ef3b-4b8b-a38a-b1d2b2cc041a</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2369,11 +2259,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>49723188-8aeb-45b3-8380-1b11246d8d41</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2451,11 +2336,6 @@
 </t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>99351a56-8bf5-4d14-8c85-856d5769d6a3</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2532,11 +2412,6 @@
 wd:Q5554167 wd:P750 wd:Q520445 .
 wd:Q5554167 wd:P449 wd:Q220072 .
 </t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>62a3d31f-6b69-43d4-b4d7-2e17c4360ae6</t>
         </is>
       </c>
     </row>
@@ -2618,11 +2493,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>7d229275-ffb7-4855-b4b2-57fc8d754f9d</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2702,11 +2572,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>b7684baf-dccd-409e-992c-4bb2d8566767</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2784,11 +2649,6 @@
 </t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>d7acf0fd-54d0-497a-88f9-66b4d7631c17</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2865,11 +2725,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>f29cb792-f635-4c32-acc8-87f19b4aa0c7</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2915,10 +2770,10 @@
         <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>4</v>
@@ -2949,11 +2804,6 @@
 </t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>10248cc7-3972-497c-94c2-b7d8b8ce82fe</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2999,10 +2849,10 @@
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
         <v>3</v>
@@ -3033,11 +2883,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>14af427a-bf33-4b79-9509-1e856a2e28c6</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3114,11 +2959,6 @@
 </t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>f720280d-e576-4654-8108-e5d1b50c020f</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3158,16 +2998,16 @@
         <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
         <v>5</v>
@@ -3200,11 +3040,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>eac912bf-14b2-472e-a9fe-475780e776d5</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3283,11 +3118,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>5ea2dded-69c9-4fdf-8071-d4739b4fd07f</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3364,11 +3194,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>f73baebe-4ce9-4c8e-94c8-1e91b263ea2d</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3446,11 +3271,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>d0e83a22-3f34-49be-9fdb-cf3cb57b4ff0</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3529,11 +3349,6 @@
 </t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>ee0ebf2b-bb8e-4a42-b5a7-6fe1acbf6df7</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3579,10 +3394,10 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
         <v>3</v>
@@ -3612,11 +3427,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>e710a8d0-df8b-4bd0-8c79-e91a4185c025</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3694,11 +3504,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>de7017f5-7acc-4186-87b8-dee9c97e284e</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3775,11 +3580,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>4fabb67b-bd73-48e2-bf92-dbd341099dc1</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3857,11 +3657,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>4fd99e42-a04d-4300-ad2f-b2557ce7d4e4</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3901,7 +3696,7 @@
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -3942,11 +3737,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>446f6175-9686-487b-9dd9-e30c5a675c1f</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4024,11 +3814,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>15499158-272f-4aa1-a6df-e5952f182283</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4103,11 +3888,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt;.
 wd:Q29644512 wd:P31 wd:Q1358919 .
 </t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>7db53c43-8657-4fc7-bb87-c2b5d689b688</t>
         </is>
       </c>
     </row>
@@ -4189,11 +3969,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>b651b98a-d54a-4f8c-b82d-f3046d372e0c</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4272,11 +4047,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>378b9156-33b2-4e72-8404-e8ee7734084d</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4354,11 +4124,6 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>913952c9-579d-4788-b18c-52fed77a874b</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4437,11 +4202,6 @@
 </t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>31869aa1-e322-4342-b5b6-238e50e0d0ad</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4487,10 +4247,10 @@
         <v>5</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
         <v>5</v>
@@ -4522,11 +4282,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>1076e5ad-1a7f-4a03-abf8-f77f9ce6ebd9</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4605,11 +4360,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>cefec37a-9f66-4439-aed9-db5102ef6b02</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4684,11 +4434,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt;.
 wd:Q2362697 wd:P556 wd:Q503601 .
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>27314f0a-80ae-489b-ac8e-3527ff1766d4</t>
         </is>
       </c>
     </row>
